--- a/artfynd/A 59293-2023 artfynd.xlsx
+++ b/artfynd/A 59293-2023 artfynd.xlsx
@@ -1056,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067826</v>
+        <v>131067473</v>
       </c>
       <c r="B5" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,37 +1067,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465891</v>
+        <v>465809</v>
       </c>
       <c r="R5" t="n">
-        <v>7046290</v>
+        <v>7046259</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,45 +1132,54 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067473</v>
+        <v>131067826</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,42 +1187,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465809</v>
+        <v>465891</v>
       </c>
       <c r="R6" t="n">
-        <v>7046259</v>
+        <v>7046290</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,44 +1247,35 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 59293-2023 artfynd.xlsx
+++ b/artfynd/A 59293-2023 artfynd.xlsx
@@ -817,7 +817,7 @@
         <v>131067454</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067473</v>
+        <v>131067826</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,42 +1067,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465809</v>
+        <v>465891</v>
       </c>
       <c r="R5" t="n">
-        <v>7046259</v>
+        <v>7046290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,54 +1127,45 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067826</v>
+        <v>131067473</v>
       </c>
       <c r="B6" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,37 +1173,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465891</v>
+        <v>465809</v>
       </c>
       <c r="R6" t="n">
-        <v>7046290</v>
+        <v>7046259</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1247,35 +1238,44 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1285,7 +1285,7 @@
         <v>131067825</v>
       </c>
       <c r="B7" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 59293-2023 artfynd.xlsx
+++ b/artfynd/A 59293-2023 artfynd.xlsx
@@ -1056,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067826</v>
+        <v>131067473</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,37 +1067,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465891</v>
+        <v>465809</v>
       </c>
       <c r="R5" t="n">
-        <v>7046290</v>
+        <v>7046259</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,45 +1132,54 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067473</v>
+        <v>131067826</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,42 +1187,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465809</v>
+        <v>465891</v>
       </c>
       <c r="R6" t="n">
-        <v>7046259</v>
+        <v>7046290</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,44 +1247,35 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 59293-2023 artfynd.xlsx
+++ b/artfynd/A 59293-2023 artfynd.xlsx
@@ -817,7 +817,7 @@
         <v>131067454</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067473</v>
+        <v>131067826</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,42 +1067,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465809</v>
+        <v>465891</v>
       </c>
       <c r="R5" t="n">
-        <v>7046259</v>
+        <v>7046290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,54 +1127,45 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067826</v>
+        <v>131067473</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,37 +1173,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465891</v>
+        <v>465809</v>
       </c>
       <c r="R6" t="n">
-        <v>7046290</v>
+        <v>7046259</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1247,35 +1238,44 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1285,7 +1285,7 @@
         <v>131067825</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 59293-2023 artfynd.xlsx
+++ b/artfynd/A 59293-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131067001</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>131067454</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>131067759</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067826</v>
+        <v>131067473</v>
       </c>
       <c r="B5" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,37 +1067,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465891</v>
+        <v>465809</v>
       </c>
       <c r="R5" t="n">
-        <v>7046290</v>
+        <v>7046259</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,45 +1132,54 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067473</v>
+        <v>131067826</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,42 +1187,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465809</v>
+        <v>465891</v>
       </c>
       <c r="R6" t="n">
-        <v>7046259</v>
+        <v>7046290</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,44 +1247,35 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1285,7 +1285,7 @@
         <v>131067825</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>131067760</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>131067002</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>131067761</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>131067474</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>131067762</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 59293-2023 artfynd.xlsx
+++ b/artfynd/A 59293-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131067001</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>131067454</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>131067759</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067473</v>
+        <v>131067826</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,42 +1067,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465809</v>
+        <v>465891</v>
       </c>
       <c r="R5" t="n">
-        <v>7046259</v>
+        <v>7046290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,54 +1127,45 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067826</v>
+        <v>131067473</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,37 +1173,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465891</v>
+        <v>465809</v>
       </c>
       <c r="R6" t="n">
-        <v>7046290</v>
+        <v>7046259</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1247,35 +1238,44 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1285,7 +1285,7 @@
         <v>131067825</v>
       </c>
       <c r="B7" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>131067760</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>131067002</v>
       </c>
       <c r="B9" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>131067761</v>
       </c>
       <c r="B10" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>131067474</v>
       </c>
       <c r="B11" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>131067762</v>
       </c>
       <c r="B12" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 59293-2023 artfynd.xlsx
+++ b/artfynd/A 59293-2023 artfynd.xlsx
@@ -1056,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067826</v>
+        <v>131067473</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,37 +1067,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465891</v>
+        <v>465809</v>
       </c>
       <c r="R5" t="n">
-        <v>7046290</v>
+        <v>7046259</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,45 +1132,54 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067473</v>
+        <v>131067826</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,42 +1187,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465809</v>
+        <v>465891</v>
       </c>
       <c r="R6" t="n">
-        <v>7046259</v>
+        <v>7046290</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,44 +1247,35 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 59293-2023 artfynd.xlsx
+++ b/artfynd/A 59293-2023 artfynd.xlsx
@@ -1056,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067473</v>
+        <v>131067826</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,42 +1067,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465809</v>
+        <v>465891</v>
       </c>
       <c r="R5" t="n">
-        <v>7046259</v>
+        <v>7046290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,54 +1127,45 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067826</v>
+        <v>131067473</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,37 +1173,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465891</v>
+        <v>465809</v>
       </c>
       <c r="R6" t="n">
-        <v>7046290</v>
+        <v>7046259</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1247,35 +1238,44 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 59293-2023 artfynd.xlsx
+++ b/artfynd/A 59293-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131067001</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>131067454</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>131067759</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>131067826</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>131067473</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>131067825</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>131067760</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>131067002</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>131067761</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>131067474</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>131067762</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 59293-2023 artfynd.xlsx
+++ b/artfynd/A 59293-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131067001</v>
+        <v>131067454</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465785</v>
+        <v>465982</v>
       </c>
       <c r="R2" t="n">
-        <v>7046277</v>
+        <v>7046411</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,14 +743,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, i riklig mängd på en gran vid en vändplan.</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,55 +766,30 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131067454</v>
+        <v>131067825</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -843,16 +811,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465982</v>
+        <v>466118</v>
       </c>
       <c r="R3" t="n">
-        <v>7046411</v>
+        <v>7046502</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,81 +853,72 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131067759</v>
+        <v>131067826</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -964,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465782</v>
+        <v>465891</v>
       </c>
       <c r="R4" t="n">
-        <v>7046264</v>
+        <v>7046290</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,43 +964,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1056,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067826</v>
+        <v>131066997</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,26 +1005,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1094,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465891</v>
+        <v>466261</v>
       </c>
       <c r="R5" t="n">
-        <v>7046290</v>
+        <v>7046588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,19 +1075,43 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1162,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067473</v>
+        <v>131066999</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,20 +1162,20 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465809</v>
+        <v>466276</v>
       </c>
       <c r="R6" t="n">
-        <v>7046259</v>
+        <v>7046581</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,24 +1205,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,26 +1223,51 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131067825</v>
+        <v>131067001</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,37 +1275,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466118</v>
+        <v>465785</v>
       </c>
       <c r="R7" t="n">
-        <v>7046502</v>
+        <v>7046277</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,19 +1349,43 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, i riklig mängd på en gran vid en vändplan.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1388,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131067760</v>
+        <v>131067002</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,17 +1439,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465777</v>
+        <v>465809</v>
       </c>
       <c r="R8" t="n">
-        <v>7046276</v>
+        <v>7046265</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,7 +1490,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, färska, i riklig mängd på en gran vid en vändplan.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,10 +1542,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131067002</v>
+        <v>131067473</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,21 +1578,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>465809</v>
       </c>
       <c r="R9" t="n">
-        <v>7046265</v>
+        <v>7046259</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1603,14 +1618,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, färska, i riklig mängd på en gran vid en vändplan.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,51 +1646,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131067761</v>
+        <v>131067474</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,14 +1701,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465773</v>
+        <v>465803</v>
       </c>
       <c r="R10" t="n">
-        <v>7046273</v>
+        <v>7046268</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1738,14 +1738,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1756,51 +1766,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131067474</v>
+        <v>131067759</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,14 +1821,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465803</v>
+        <v>465782</v>
       </c>
       <c r="R11" t="n">
-        <v>7046268</v>
+        <v>7046264</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1873,24 +1858,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:47</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:47</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1901,26 +1876,51 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131067762</v>
+        <v>131067760</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465769</v>
+        <v>465777</v>
       </c>
       <c r="R12" t="n">
-        <v>7046270</v>
+        <v>7046276</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2049,6 +2049,276 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131067761</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långan Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>465773</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7046273</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131067762</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långan Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>465769</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7046270</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59293-2023 artfynd.xlsx
+++ b/artfynd/A 59293-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067454</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067825</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067826</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066997</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,6 +1286,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066999</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1400,6 +1430,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067001</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1539,6 +1574,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067002</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1659,6 +1699,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067473</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1779,6 +1824,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067474</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1914,6 +1964,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067759</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2049,6 +2104,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067760</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2184,6 +2244,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067761</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2319,8 +2384,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067762</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>